--- a/artfynd/A 16752-2022 artfynd.xlsx
+++ b/artfynd/A 16752-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 16752-2022 artfynd.xlsx
+++ b/artfynd/A 16752-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>94901882</v>
       </c>
       <c r="B2" t="n">
-        <v>77532</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79351</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>821097.9416792542</v>
+        <v>821098</v>
       </c>
       <c r="R2" t="n">
-        <v>7302230.194723141</v>
+        <v>7302231</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -791,57 +786,52 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>95050814</v>
+        <v>114569618</v>
       </c>
       <c r="B3" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hällarna, Sunderbyns soptipp, Nb</t>
+          <t>Norrbotten, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>821156.2821227338</v>
+        <v>821375</v>
       </c>
       <c r="R3" t="n">
-        <v>7302218.027656811</v>
+        <v>7302287</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,22 +855,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-07-15</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-07-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,76 +869,70 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Frida Snell</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Frida Snell, Mats Bergquist</t>
+          <t>Väg och Miljö AB, Ursula Zinko, Klas Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>94901819</v>
+        <v>114569705</v>
       </c>
       <c r="B4" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hällarna, Sunderbyns soptipp, Nb</t>
+          <t>Norrbotten, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>821097.9416792542</v>
+        <v>821383</v>
       </c>
       <c r="R4" t="n">
-        <v>7302230.194723141</v>
+        <v>7302287</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,22 +956,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-07-15</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>08:40</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-07-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:20</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,34 +970,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Mats Bergquist</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mats Bergquist, Frida Snell</t>
+          <t>Väg och Miljö AB, Ursula Zinko, Klas Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>95050827</v>
+        <v>94901819</v>
       </c>
       <c r="B5" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1069,13 +1027,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>821096.2151170436</v>
+        <v>821098</v>
       </c>
       <c r="R5" t="n">
-        <v>7302290.238222037</v>
+        <v>7302231</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1104,7 +1062,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,12 +1072,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Flera stjälkar</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,69 +1088,64 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Frida Snell</t>
+          <t>Mats Bergquist</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Frida Snell, Mats Bergquist</t>
+          <t>Mats Bergquist, Frida Snell</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>114569618</v>
+        <v>95050814</v>
       </c>
       <c r="B6" t="n">
-        <v>79099</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Norrbotten, Nb</t>
+          <t>Hällarna, Sunderbyns soptipp, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>821375</v>
+        <v>821156</v>
       </c>
       <c r="R6" t="n">
-        <v>7302287</v>
+        <v>7302218</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1221,12 +1169,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-06-15</t>
+          <t>2021-07-15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-06-15</t>
+          <t>2021-07-15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,75 +1183,71 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Frida Snell</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Ursula Zinko, Klas Andersson</t>
+          <t>Frida Snell, Mats Bergquist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>114569705</v>
+        <v>95050827</v>
       </c>
       <c r="B7" t="n">
-        <v>79099</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Norrbotten, Nb</t>
+          <t>Hällarna, Sunderbyns soptipp, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>821383</v>
+        <v>821096</v>
       </c>
       <c r="R7" t="n">
-        <v>7302287</v>
+        <v>7302291</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1327,12 +1271,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-06-15</t>
+          <t>2021-07-15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-06-15</t>
+          <t>2021-07-15</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Flera stjälkar</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1341,21 +1290,129 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Frida Snell</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Klas Andersson, Ursula Zinko, Väg och Miljö AB</t>
+          <t>Frida Snell, Mats Bergquist</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>95050848</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Myren, Sunderbyns soptipp, Nb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>821014</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7302148</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Nederluleå</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2021-07-15</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2021-07-15</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Flera stjälkar</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Frida Snell</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Frida Snell, Mats Bergquist</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16752-2022 artfynd.xlsx
+++ b/artfynd/A 16752-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94901882</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114569618</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -985,6 +1000,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114569705</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1097,6 +1117,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94901819</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1199,6 +1224,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95050814</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1306,6 +1336,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95050827</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1413,8 +1448,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95050848</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>